--- a/web/Importaciones/ImportarCalifAlumnos.xlsx
+++ b/web/Importaciones/ImportarCalifAlumnos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paola\Documents\NetBeansProjects\Titulos\web\Importaciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DC5026-081C-4519-9BD6-0D18D21CB14E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C44F88E-30D0-4DA5-BF42-F623D6B08ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{ACE2E2C5-6598-4E41-BFA9-0B9C356CE48A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{ACE2E2C5-6598-4E41-BFA9-0B9C356CE48A}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificaciones" sheetId="3" r:id="rId1"/>
@@ -806,7 +806,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -864,13 +864,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -933,9 +930,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -973,7 +970,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1079,7 +1076,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1221,7 +1218,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1247,11 +1244,11 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="21"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="20"/>
       <c r="J1" s="15" t="s">
         <v>30</v>
       </c>
@@ -1269,16 +1266,16 @@
     </row>
     <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="29"/>
+      <c r="C2" s="28"/>
       <c r="D2" s="20"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
       <c r="J2" s="3">
         <v>70</v>
       </c>
@@ -1292,14 +1289,14 @@
     </row>
     <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="20"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
       <c r="J3" s="6">
         <v>71</v>
       </c>
@@ -1313,16 +1310,16 @@
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="29"/>
+      <c r="C4" s="28"/>
       <c r="D4" s="20"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
       <c r="J4" s="9">
         <v>72</v>
       </c>
@@ -1338,13 +1335,13 @@
       <c r="A5" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
       <c r="J5" s="9">
         <v>73</v>
       </c>
@@ -1364,9 +1361,9 @@
       <c r="A6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="22"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="19"/>
       <c r="J6" s="9">
         <v>74</v>
@@ -1387,9 +1384,9 @@
       <c r="A7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="23"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="22"/>
       <c r="J7" s="9">
         <v>75</v>
       </c>
@@ -1409,9 +1406,9 @@
       <c r="A8" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="23"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="22"/>
       <c r="J8" s="9">
         <v>76</v>
       </c>
@@ -1437,7 +1434,7 @@
       <c r="C9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="23" t="s">
         <v>42</v>
       </c>
       <c r="E9" s="18" t="s">
@@ -1524,10 +1521,10 @@
       <c r="J14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="25" t="s">
+      <c r="L14" s="24" t="s">
         <v>45</v>
       </c>
       <c r="M14" s="16"/>
@@ -1540,10 +1537,10 @@
       <c r="J15" s="9">
         <v>105</v>
       </c>
-      <c r="K15" s="25" t="s">
+      <c r="K15" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L15" s="25" t="s">
+      <c r="L15" s="24" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="16"/>
@@ -1553,24 +1550,24 @@
       <c r="Q15" s="16"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
     </row>
     <row r="17" spans="10:13" x14ac:dyDescent="0.25">
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" spans="10:13" x14ac:dyDescent="0.25">
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1586,8 +1583,8 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="F4:H5"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:D5" xr:uid="{9A5BA7BA-D754-47C3-AEB8-74488BD2EDB2}">
+  <dataValidations count="3">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5" xr:uid="{9A5BA7BA-D754-47C3-AEB8-74488BD2EDB2}">
       <formula1>6</formula1>
       <formula2>20</formula2>
     </dataValidation>
@@ -1595,6 +1592,10 @@
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:C5" xr:uid="{CA485020-14E9-4F4B-80E0-176CDB883360}">
+      <formula1>2</formula1>
+      <formula2>20</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
